--- a/starter-workbook.xlsx
+++ b/starter-workbook.xlsx
@@ -1,57 +1,111 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\modern-excel-demo-day-america250\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E551152-7D8F-4EC0-AB3F-54E48B938DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start here" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Start here" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>Stringfest Analytics</t>
+  </si>
+  <si>
+    <t>Modern Excel Demo Day — America 250 Edition</t>
+  </si>
+  <si>
+    <t>Starter workbook — follow along live</t>
+  </si>
+  <si>
+    <t>Today we'll turn a messy 2-page PDF of U.S. census data into a refreshable analytical model.</t>
+  </si>
+  <si>
+    <t>What you'll do:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  1. Pull the PDF into Power Query and clean it (combine pages, drop totals, unpivot decades)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2. Use an AI prompt to rewrite the auto-generated M code so it's actually readable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3. Merge in Census regions as a dimension table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  4. Build a PivotTable + slicer to explore regional shifts over 220 years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  5. Drop in one Python in Excel cell that produces a chart Excel can't make natively</t>
+  </si>
+  <si>
+    <t>Source file:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  usstpopulation17902010.pdf  —  U.S. Census Bureau, 1790–2010 state populations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  (prepared by State Library of Iowa, State Data Center Program)</t>
+  </si>
+  <si>
+    <t>How to start the Power Query import:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Data tab  →  Get Data  →  From File  →  From PDF  →  select the file</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFCF3338"/>
       <name val="Arial Black"/>
-      <b val="1"/>
-      <color rgb="00CF3338"/>
-      <sz val="14"/>
     </font>
     <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFCF3338"/>
       <name val="Arial Black"/>
-      <b val="1"/>
-      <color rgb="00CF3338"/>
-      <sz val="20"/>
     </font>
     <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF707070"/>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00707070"/>
-      <sz val="12"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF1F2120"/>
       <name val="Arial"/>
-      <color rgb="001F2120"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -70,86 +124,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -437,160 +432,114 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stringfest Analytics</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Modern Excel Demo Day — America 250 Edition</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Starter workbook — follow along live</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Today we'll turn a messy 2-page PDF of U.S. census data into a refreshable analytical model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>What you'll do:</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. Pull the PDF into Power Query and clean it (combine pages, drop totals, unpivot decades)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. Use an AI prompt to rewrite the auto-generated M code so it's actually readable</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  3. Merge in Census regions as a dimension table</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  4. Build a PivotTable + slicer to explore regional shifts over 220 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  5. Drop in one Python in Excel cell that produces a chart Excel can't make natively</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Source file:</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  usstpopulation17902010.pdf  —  U.S. Census Bureau, 1790–2010 state populations</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (prepared by State Library of Iowa, State Data Center Program)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>How to start the Power Query import:</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Data tab  →  Get Data  →  From File  →  From PDF  →  select the file</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>You'll get tables labeled Table001, Table002 — those are the two pages.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Select both and click Transform Data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>When you finish, your workbook should match the one in 02_finished_workbook.xlsx.</t>
-        </is>
-      </c>
+    <row r="1" spans="1:1" ht="21.35" x14ac:dyDescent="0.9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="30.7" x14ac:dyDescent="1.3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15.35" x14ac:dyDescent="0.5">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A5" s="4"/>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A6" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A8" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A9" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A10" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A11" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A12" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A13" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A14" s="4"/>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A15" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A16" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A17" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A18" s="4"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A19" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A20" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A21" s="4"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A22" s="4"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A23" s="4"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A24" s="4"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.5">
+      <c r="A25" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
